--- a/SGC-CKN/Excel/b795b8da-18bb-4585-ab77-fb0bf197803a_Thi_công_cọc_khoan_nhồi_P8-3_D800_29-03-2026.xlsx
+++ b/SGC-CKN/Excel/b795b8da-18bb-4585-ab77-fb0bf197803a_Thi_công_cọc_khoan_nhồi_P8-3_D800_29-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="76">
   <si>
     <t>Dự án</t>
   </si>
@@ -102,7 +102,7 @@
 28/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">13:20
+    <t xml:space="preserve">13:30
 28/03/2026</t>
   </si>
   <si>
@@ -143,22 +143,18 @@
     <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
   </si>
   <si>
-    <t xml:space="preserve">15:06
+    <t xml:space="preserve">15:01
 28/03/2026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16:02
-28/03/2026</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
     <t xml:space="preserve">16:00
 28/03/2026</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
     <t xml:space="preserve">16:50
@@ -1259,13 +1255,13 @@
         <v>7.25</v>
       </c>
       <c r="H11" s="5">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="I11" s="5">
         <v>7.25</v>
       </c>
       <c r="J11" s="8">
-        <v>21.75</v>
+        <v>14.5</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1326,16 +1322,16 @@
         <v>9.05</v>
       </c>
       <c r="G13" s="13">
-        <v>12.92</v>
+        <v>-17.92</v>
       </c>
       <c r="H13" s="13">
         <v>0.82</v>
       </c>
       <c r="I13" s="13">
-        <v>3.87</v>
-      </c>
-      <c r="J13" s="12">
-        <v>4.74</v>
+        <v>26.97</v>
+      </c>
+      <c r="J13" s="8">
+        <v>33.02</v>
       </c>
       <c r="K13" s="14" t="s">
         <v>30</v>
@@ -1358,19 +1354,19 @@
         <v>42</v>
       </c>
       <c r="F14" s="16">
-        <v>12.92</v>
+        <v>-17.92</v>
       </c>
       <c r="G14" s="16">
-        <v>24.93</v>
+        <v>-21.33</v>
       </c>
       <c r="H14" s="16">
-        <v>0.93</v>
+        <v>0.98</v>
       </c>
       <c r="I14" s="16">
-        <v>12.01</v>
-      </c>
-      <c r="J14" s="8">
-        <v>12.87</v>
+        <v>3.41</v>
+      </c>
+      <c r="J14" s="12">
+        <v>3.47</v>
       </c>
       <c r="K14" s="17" t="s">
         <v>30</v>
@@ -1387,25 +1383,25 @@
         <v>44</v>
       </c>
       <c r="D15" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="E15" s="21" t="s">
         <v>45</v>
       </c>
-      <c r="E15" s="21" t="s">
-        <v>46</v>
-      </c>
       <c r="F15" s="19">
-        <v>24.93</v>
+        <v>-21.33</v>
       </c>
       <c r="G15" s="19">
-        <v>28.7</v>
+        <v>-28.7</v>
       </c>
       <c r="H15" s="19">
         <v>0.83</v>
       </c>
       <c r="I15" s="19">
-        <v>3.77</v>
-      </c>
-      <c r="J15" s="12">
-        <v>4.52</v>
+        <v>7.37</v>
+      </c>
+      <c r="J15" s="8">
+        <v>8.84</v>
       </c>
       <c r="K15" s="20" t="s">
         <v>30</v>
@@ -1413,34 +1409,34 @@
     </row>
     <row r="16" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="22" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B16" s="22" t="s">
         <v>11</v>
       </c>
       <c r="C16" s="23" t="s">
+        <v>47</v>
+      </c>
+      <c r="D16" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="D16" s="24" t="s">
+      <c r="E16" s="24" t="s">
         <v>49</v>
       </c>
-      <c r="E16" s="24" t="s">
-        <v>50</v>
-      </c>
       <c r="F16" s="22">
-        <v>28.7</v>
+        <v>-28.7</v>
       </c>
       <c r="G16" s="22">
-        <v>35.44</v>
+        <v>-35.41</v>
       </c>
       <c r="H16" s="22">
         <v>0.65</v>
       </c>
       <c r="I16" s="22">
-        <v>6.74</v>
+        <v>6.71</v>
       </c>
       <c r="J16" s="8">
-        <v>10.37</v>
+        <v>10.32</v>
       </c>
       <c r="K16" s="23" t="s">
         <v>30</v>
@@ -1448,34 +1444,34 @@
     </row>
     <row r="17" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="25" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B17" s="25" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="D17" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="D17" s="27" t="s">
+      <c r="E17" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="E17" s="27" t="s">
-        <v>54</v>
-      </c>
       <c r="F17" s="25">
-        <v>35.44</v>
+        <v>-35.41</v>
       </c>
       <c r="G17" s="25">
-        <v>36.89</v>
+        <v>-36.89</v>
       </c>
       <c r="H17" s="25">
         <v>1.32</v>
       </c>
       <c r="I17" s="25">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="J17" s="12">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
       <c r="K17" s="26" t="s">
         <v>30</v>
@@ -1483,22 +1479,22 @@
     </row>
     <row r="18" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="28" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B18" s="28" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="29" t="s">
+        <v>55</v>
+      </c>
+      <c r="D18" s="30" t="s">
         <v>56</v>
       </c>
-      <c r="D18" s="30" t="s">
+      <c r="E18" s="30" t="s">
         <v>57</v>
       </c>
-      <c r="E18" s="30" t="s">
-        <v>58</v>
-      </c>
       <c r="F18" s="28">
-        <v>36.89</v>
+        <v>-36.89</v>
       </c>
       <c r="G18" s="28">
         <v>39.5</v>
@@ -1507,10 +1503,10 @@
         <v>2.07</v>
       </c>
       <c r="I18" s="28">
-        <v>2.61</v>
-      </c>
-      <c r="J18" s="12">
-        <v>1.26</v>
+        <v>76.39</v>
+      </c>
+      <c r="J18" s="8">
+        <v>36.96</v>
       </c>
       <c r="K18" s="29" t="s">
         <v>30</v>
@@ -1518,19 +1514,19 @@
     </row>
     <row r="19" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="31" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B19" s="31" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="D19" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="D19" s="33" t="s">
+      <c r="E19" s="33" t="s">
         <v>61</v>
-      </c>
-      <c r="E19" s="33" t="s">
-        <v>62</v>
       </c>
       <c r="F19" s="31">
         <v>39.5</v>
@@ -1553,19 +1549,19 @@
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="34" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B20" s="34" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="35" t="s">
+        <v>63</v>
+      </c>
+      <c r="D20" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="D20" s="36" t="s">
+      <c r="E20" s="36" t="s">
         <v>65</v>
-      </c>
-      <c r="E20" s="36" t="s">
-        <v>66</v>
       </c>
       <c r="F20" s="34">
         <v>43.92</v>
@@ -1588,7 +1584,7 @@
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="38" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B23" s="38"/>
       <c r="C23" s="38"/>
@@ -1694,31 +1690,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>74</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1741,13 +1737,13 @@
         <v>7.25</v>
       </c>
       <c r="G2" s="5">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="H2" s="5">
         <v>7.25</v>
       </c>
       <c r="I2" s="8">
-        <v>21.75</v>
+        <v>14.5</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1796,16 +1792,16 @@
         <v>9.05</v>
       </c>
       <c r="F4" s="13">
-        <v>12.92</v>
+        <v>-17.92</v>
       </c>
       <c r="G4" s="13">
         <v>0.82</v>
       </c>
       <c r="H4" s="13">
-        <v>3.87</v>
-      </c>
-      <c r="I4" s="12">
-        <v>4.74</v>
+        <v>26.97</v>
+      </c>
+      <c r="I4" s="8">
+        <v>33.02</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1822,19 +1818,19 @@
         <v>1</v>
       </c>
       <c r="E5" s="16">
-        <v>12.92</v>
+        <v>-17.92</v>
       </c>
       <c r="F5" s="16">
-        <v>24.93</v>
+        <v>-21.33</v>
       </c>
       <c r="G5" s="16">
-        <v>0.93</v>
+        <v>0.98</v>
       </c>
       <c r="H5" s="16">
-        <v>12.01</v>
-      </c>
-      <c r="I5" s="8">
-        <v>12.87</v>
+        <v>3.41</v>
+      </c>
+      <c r="I5" s="12">
+        <v>3.47</v>
       </c>
     </row>
     <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1851,19 +1847,19 @@
         <v>1</v>
       </c>
       <c r="E6" s="19">
-        <v>24.93</v>
+        <v>-21.33</v>
       </c>
       <c r="F6" s="19">
-        <v>28.7</v>
+        <v>-28.7</v>
       </c>
       <c r="G6" s="19">
         <v>0.83</v>
       </c>
       <c r="H6" s="19">
-        <v>3.77</v>
-      </c>
-      <c r="I6" s="12">
-        <v>4.52</v>
+        <v>7.37</v>
+      </c>
+      <c r="I6" s="8">
+        <v>8.84</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1874,25 +1870,25 @@
         <v>11</v>
       </c>
       <c r="C7" s="23" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="D7" s="22">
         <v>1</v>
       </c>
       <c r="E7" s="22">
-        <v>28.7</v>
+        <v>-28.7</v>
       </c>
       <c r="F7" s="22">
-        <v>35.44</v>
+        <v>-35.41</v>
       </c>
       <c r="G7" s="22">
         <v>0.65</v>
       </c>
       <c r="H7" s="22">
-        <v>6.74</v>
+        <v>6.71</v>
       </c>
       <c r="I7" s="8">
-        <v>10.37</v>
+        <v>10.32</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1903,25 +1899,25 @@
         <v>11</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D8" s="25">
         <v>1</v>
       </c>
       <c r="E8" s="25">
-        <v>35.44</v>
+        <v>-35.41</v>
       </c>
       <c r="F8" s="25">
-        <v>36.89</v>
+        <v>-36.89</v>
       </c>
       <c r="G8" s="25">
         <v>1.32</v>
       </c>
       <c r="H8" s="25">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="I8" s="12">
-        <v>1.1</v>
+        <v>1.12</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1932,13 +1928,13 @@
         <v>11</v>
       </c>
       <c r="C9" s="29" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D9" s="28">
         <v>1</v>
       </c>
       <c r="E9" s="28">
-        <v>36.89</v>
+        <v>-36.89</v>
       </c>
       <c r="F9" s="28">
         <v>39.5</v>
@@ -1947,10 +1943,10 @@
         <v>2.07</v>
       </c>
       <c r="H9" s="28">
-        <v>2.61</v>
-      </c>
-      <c r="I9" s="12">
-        <v>1.26</v>
+        <v>76.39</v>
+      </c>
+      <c r="I9" s="8">
+        <v>36.96</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1961,7 +1957,7 @@
         <v>11</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D10" s="31">
         <v>1</v>
@@ -1990,7 +1986,7 @@
         <v>11</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D11" s="34">
         <v>1</v>
@@ -2013,7 +2009,7 @@
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="39" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B12" s="40" t="s">
         <v>30</v>
@@ -2031,13 +2027,13 @@
         <v>44.8</v>
       </c>
       <c r="G12" s="40">
-        <v>10.65</v>
+        <v>10.87</v>
       </c>
       <c r="H12" s="40">
-        <v>44.8</v>
+        <v>136.68</v>
       </c>
       <c r="I12" s="40">
-        <v>4.21</v>
+        <v>12.58</v>
       </c>
     </row>
   </sheetData>

--- a/SGC-CKN/Excel/b795b8da-18bb-4585-ab77-fb0bf197803a_Thi_công_cọc_khoan_nhồi_P8-3_D800_29-03-2026.xlsx
+++ b/SGC-CKN/Excel/b795b8da-18bb-4585-ab77-fb0bf197803a_Thi_công_cọc_khoan_nhồi_P8-3_D800_29-03-2026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="75">
   <si>
     <t>Dự án</t>
   </si>
@@ -95,7 +95,7 @@
     <t>1</t>
   </si>
   <si>
-    <t>Sét lẫn hữu cơ, xám nâu, xám đen TT dẻo chảy</t>
+    <t>Sét lẫn hữu cơ, xám nâu, xám đen, xám trắng, xám xanh TT dẻo chảy</t>
   </si>
   <si>
     <t xml:space="preserve">13:00
@@ -112,7 +112,7 @@
     <t>2</t>
   </si>
   <si>
-    <t>Cát pha xám ghi, xám nâu TT dẻo</t>
+    <t>Cát pha, xám ghi, xám nâu, xám vàng, TT dẻo</t>
   </si>
   <si>
     <t xml:space="preserve">13:31
@@ -140,7 +140,7 @@
     <t>4</t>
   </si>
   <si>
-    <t>Sét xám vàng, nâu vàng xám xanh TT nửa cứng</t>
+    <t>Sét xám vàng, nâu vàng, xám xanh, TT nửa cứng</t>
   </si>
   <si>
     <t xml:space="preserve">15:01
@@ -154,7 +154,7 @@
     <t>5</t>
   </si>
   <si>
-    <t>Cát thô vừa, xám vàng, xám xanh TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
+    <t>Cát thô vừa, xám vàng, xám xanh, TT chặt lẫn sỏi sạn, có chỗ là cát hạt nhỏ, bụi</t>
   </si>
   <si>
     <t xml:space="preserve">16:50
@@ -164,7 +164,7 @@
     <t>6</t>
   </si>
   <si>
-    <t>Cát thô, xám vàng, xám xanh, xám nâu KC chặt</t>
+    <t>Cát thô, xám vàng, xám xanh, xám nâu, KC chặt</t>
   </si>
   <si>
     <t xml:space="preserve">16:51
@@ -178,7 +178,7 @@
     <t>7</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh, TT rất chặt</t>
+    <t>Sỏi xám vàng, nâu vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">17:31
@@ -192,7 +192,7 @@
     <t>8</t>
   </si>
   <si>
-    <t>TK-16.1.Cát xạm, xám vàng, xám xanh, TT rất chặt</t>
+    <t>Cát xạm, xám vàng, xám xanh, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">18:51
@@ -206,9 +206,6 @@
     <t>9</t>
   </si>
   <si>
-    <t>Sỏi xám vàng, xám xanh TT rất chặt</t>
-  </si>
-  <si>
     <t xml:space="preserve">20:56
 28/03/2026</t>
   </si>
@@ -220,7 +217,7 @@
     <t>10</t>
   </si>
   <si>
-    <t>Cuội đa màu sắc TT rất chặt</t>
+    <t>Cuội đa màu sắc, TT rất chặt</t>
   </si>
   <si>
     <t xml:space="preserve">22:41
@@ -1319,7 +1316,7 @@
         <v>38</v>
       </c>
       <c r="F13" s="13">
-        <v>9.05</v>
+        <v>-9.05</v>
       </c>
       <c r="G13" s="13">
         <v>-17.92</v>
@@ -1328,10 +1325,10 @@
         <v>0.82</v>
       </c>
       <c r="I13" s="13">
-        <v>26.97</v>
+        <v>8.87</v>
       </c>
       <c r="J13" s="8">
-        <v>33.02</v>
+        <v>10.86</v>
       </c>
       <c r="K13" s="14" t="s">
         <v>30</v>
@@ -1497,16 +1494,16 @@
         <v>-36.89</v>
       </c>
       <c r="G18" s="28">
-        <v>39.5</v>
+        <v>-39.5</v>
       </c>
       <c r="H18" s="28">
         <v>2.07</v>
       </c>
       <c r="I18" s="28">
-        <v>76.39</v>
-      </c>
-      <c r="J18" s="8">
-        <v>36.96</v>
+        <v>2.61</v>
+      </c>
+      <c r="J18" s="12">
+        <v>1.26</v>
       </c>
       <c r="K18" s="29" t="s">
         <v>30</v>
@@ -1520,16 +1517,16 @@
         <v>11</v>
       </c>
       <c r="C19" s="32" t="s">
+        <v>51</v>
+      </c>
+      <c r="D19" s="33" t="s">
         <v>59</v>
       </c>
-      <c r="D19" s="33" t="s">
+      <c r="E19" s="33" t="s">
         <v>60</v>
       </c>
-      <c r="E19" s="33" t="s">
-        <v>61</v>
-      </c>
       <c r="F19" s="31">
-        <v>39.5</v>
+        <v>-39.5</v>
       </c>
       <c r="G19" s="31">
         <v>43.92</v>
@@ -1549,25 +1546,25 @@
     </row>
     <row r="20" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="34" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B20" s="34" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="D20" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="D20" s="36" t="s">
+      <c r="E20" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="E20" s="36" t="s">
-        <v>65</v>
-      </c>
       <c r="F20" s="34">
-        <v>43.92</v>
+        <v>-43.92</v>
       </c>
       <c r="G20" s="34">
-        <v>44.8</v>
+        <v>-44.8</v>
       </c>
       <c r="H20" s="34">
         <v>1.32</v>
@@ -1584,7 +1581,7 @@
     </row>
     <row r="23" ht="25" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="38" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B23" s="38"/>
       <c r="C23" s="38"/>
@@ -1690,31 +1687,31 @@
   <sheetData>
     <row r="1" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="3" t="s">
         <v>73</v>
-      </c>
-      <c r="I1" s="3" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="2" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1789,7 +1786,7 @@
         <v>1</v>
       </c>
       <c r="E4" s="13">
-        <v>9.05</v>
+        <v>-9.05</v>
       </c>
       <c r="F4" s="13">
         <v>-17.92</v>
@@ -1798,10 +1795,10 @@
         <v>0.82</v>
       </c>
       <c r="H4" s="13">
-        <v>26.97</v>
+        <v>8.87</v>
       </c>
       <c r="I4" s="8">
-        <v>33.02</v>
+        <v>10.86</v>
       </c>
     </row>
     <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1937,16 +1934,16 @@
         <v>-36.89</v>
       </c>
       <c r="F9" s="28">
-        <v>39.5</v>
+        <v>-39.5</v>
       </c>
       <c r="G9" s="28">
         <v>2.07</v>
       </c>
       <c r="H9" s="28">
-        <v>76.39</v>
-      </c>
-      <c r="I9" s="8">
-        <v>36.96</v>
+        <v>2.61</v>
+      </c>
+      <c r="I9" s="12">
+        <v>1.26</v>
       </c>
     </row>
     <row r="10" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1957,13 +1954,13 @@
         <v>11</v>
       </c>
       <c r="C10" s="32" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="D10" s="31">
         <v>1</v>
       </c>
       <c r="E10" s="31">
-        <v>39.5</v>
+        <v>-39.5</v>
       </c>
       <c r="F10" s="31">
         <v>43.92</v>
@@ -1986,16 +1983,16 @@
         <v>11</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D11" s="34">
         <v>1</v>
       </c>
       <c r="E11" s="34">
-        <v>43.92</v>
+        <v>-43.92</v>
       </c>
       <c r="F11" s="34">
-        <v>44.8</v>
+        <v>-44.8</v>
       </c>
       <c r="G11" s="34">
         <v>1.32</v>
@@ -2009,7 +2006,7 @@
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="39" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B12" s="40" t="s">
         <v>30</v>
@@ -2024,16 +2021,16 @@
         <v>0</v>
       </c>
       <c r="F12" s="40">
-        <v>44.8</v>
+        <v>-44.8</v>
       </c>
       <c r="G12" s="40">
         <v>10.87</v>
       </c>
       <c r="H12" s="40">
-        <v>136.68</v>
+        <v>44.8</v>
       </c>
       <c r="I12" s="40">
-        <v>12.58</v>
+        <v>4.12</v>
       </c>
     </row>
   </sheetData>
